--- a/Experiments/outputs/scenario_6.xlsx
+++ b/Experiments/outputs/scenario_6.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1326.490187664834</v>
+        <v>1119.204239711576</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5429079532623291</v>
+        <v>3.11858081817627</v>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>405</v>
       </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="H2" t="n">
-        <v>2450.024968546591</v>
+        <v>2010.832507486917</v>
       </c>
       <c r="I2" t="n">
-        <v>1.530633926391602</v>
+        <v>19.52159810066223</v>
       </c>
       <c r="J2" t="n">
-        <v>420</v>
+        <v>449</v>
       </c>
       <c r="K2" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="L2" t="n">
-        <v>520</v>
+        <v>456</v>
       </c>
       <c r="M2" t="n">
-        <v>6805.509724626897</v>
+        <v>5999.521350106113</v>
       </c>
       <c r="N2" t="n">
-        <v>5.335360050201416</v>
+        <v>5.036226987838745</v>
       </c>
       <c r="O2" t="n">
-        <v>1908</v>
+        <v>2643</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>6111</v>
+        <v>8077</v>
       </c>
       <c r="R2" t="n">
-        <v>0.805085843479923</v>
+        <v>0.8134510781111262</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6399939067487102</v>
+        <v>0.6648345109312176</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1454.066759559008</v>
+        <v>1257.670103718104</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6737687587738037</v>
+        <v>2.790680885314941</v>
       </c>
       <c r="E3" t="n">
-        <v>312</v>
+        <v>358</v>
       </c>
       <c r="F3" t="n">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H3" t="n">
-        <v>2695.810914829384</v>
+        <v>2210.793248900894</v>
       </c>
       <c r="I3" t="n">
-        <v>2.074115991592407</v>
+        <v>20.05058813095093</v>
       </c>
       <c r="J3" t="n">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="K3" t="n">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="L3" t="n">
-        <v>502</v>
+        <v>456</v>
       </c>
       <c r="M3" t="n">
-        <v>6845.109432196788</v>
+        <v>5953.330318240592</v>
       </c>
       <c r="N3" t="n">
-        <v>6.748040914535522</v>
+        <v>4.250984907150269</v>
       </c>
       <c r="O3" t="n">
-        <v>1824</v>
+        <v>2685</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>5824</v>
+        <v>8244</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7875758197933797</v>
+        <v>0.7887451163486277</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6061697856648841</v>
+        <v>0.6286459627265806</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1445.394438448945</v>
+        <v>1173.161848379875</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5609350204467773</v>
+        <v>3.411746978759766</v>
       </c>
       <c r="E4" t="n">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="F4" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="H4" t="n">
-        <v>2452.964031806073</v>
+        <v>2047.7306819164</v>
       </c>
       <c r="I4" t="n">
-        <v>1.442651748657227</v>
+        <v>20.66316390037537</v>
       </c>
       <c r="J4" t="n">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="K4" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="L4" t="n">
-        <v>503</v>
+        <v>441</v>
       </c>
       <c r="M4" t="n">
-        <v>6698.762625907772</v>
+        <v>5871.173342928741</v>
       </c>
       <c r="N4" t="n">
-        <v>4.925543069839478</v>
+        <v>167.8831243515015</v>
       </c>
       <c r="O4" t="n">
-        <v>1852</v>
+        <v>2671</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>5903</v>
+        <v>8116</v>
       </c>
       <c r="R4" t="n">
-        <v>0.784229637745512</v>
+        <v>0.8001827267129092</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6338183379839253</v>
+        <v>0.651222922180846</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1382.13694289885</v>
+        <v>1140.160190888937</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4841511249542236</v>
+        <v>4.539684057235718</v>
       </c>
       <c r="E5" t="n">
-        <v>340</v>
+        <v>404</v>
       </c>
       <c r="F5" t="n">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H5" t="n">
-        <v>2624.813469148484</v>
+        <v>2027.529417441925</v>
       </c>
       <c r="I5" t="n">
-        <v>1.762821674346924</v>
+        <v>24.31521701812744</v>
       </c>
       <c r="J5" t="n">
-        <v>384</v>
+        <v>443</v>
       </c>
       <c r="K5" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="L5" t="n">
-        <v>492</v>
+        <v>445</v>
       </c>
       <c r="M5" t="n">
-        <v>6823.376415946379</v>
+        <v>5951.853439542682</v>
       </c>
       <c r="N5" t="n">
-        <v>4.133182048797607</v>
+        <v>4.562679052352905</v>
       </c>
       <c r="O5" t="n">
-        <v>1884</v>
+        <v>2619</v>
       </c>
       <c r="P5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>5980</v>
+        <v>7963</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7974409062837621</v>
+        <v>0.8084361111256561</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6153204353471928</v>
+        <v>0.6593448682772484</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1415.768848574634</v>
+        <v>1125.190684624387</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4474880695343018</v>
+        <v>2.955568313598633</v>
       </c>
       <c r="E6" t="n">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="F6" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H6" t="n">
-        <v>2596.371306318881</v>
+        <v>2048.796219296356</v>
       </c>
       <c r="I6" t="n">
-        <v>1.515208959579468</v>
+        <v>20.53065896034241</v>
       </c>
       <c r="J6" t="n">
-        <v>395</v>
+        <v>447</v>
       </c>
       <c r="K6" t="n">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
-        <v>500</v>
+        <v>452</v>
       </c>
       <c r="M6" t="n">
-        <v>6778.946356272306</v>
+        <v>5934.646516018621</v>
       </c>
       <c r="N6" t="n">
-        <v>4.660477876663208</v>
+        <v>5.285599231719971</v>
       </c>
       <c r="O6" t="n">
-        <v>1893</v>
+        <v>2635</v>
       </c>
       <c r="P6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>6059</v>
+        <v>8039</v>
       </c>
       <c r="R6" t="n">
-        <v>0.791152079664316</v>
+        <v>0.8104030827131312</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6169948588077326</v>
+        <v>0.6547736729110476</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1409.581448170124</v>
+        <v>1164.290874916209</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4527690410614014</v>
+        <v>2.580812931060791</v>
       </c>
       <c r="E7" t="n">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="F7" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H7" t="n">
-        <v>2618.729148161932</v>
+        <v>2103.761917966032</v>
       </c>
       <c r="I7" t="n">
-        <v>1.450294017791748</v>
+        <v>22.83429980278015</v>
       </c>
       <c r="J7" t="n">
-        <v>391</v>
+        <v>448</v>
       </c>
       <c r="K7" t="n">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="L7" t="n">
-        <v>503</v>
+        <v>459</v>
       </c>
       <c r="M7" t="n">
-        <v>6860.399116678645</v>
+        <v>6024.836989640529</v>
       </c>
       <c r="N7" t="n">
-        <v>4.641980171203613</v>
+        <v>6.186359167098999</v>
       </c>
       <c r="O7" t="n">
-        <v>1859</v>
+        <v>2635</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="n">
-        <v>5984</v>
+        <v>7981</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7945336088765999</v>
+        <v>0.8067514727920172</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6182832655034</v>
+        <v>0.6508184500952693</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1237.232550877783</v>
+        <v>1179.863559611644</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4557528495788574</v>
+        <v>4.027186870574951</v>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="F8" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="H8" t="n">
-        <v>2602.931016959888</v>
+        <v>1982.801225798358</v>
       </c>
       <c r="I8" t="n">
-        <v>1.565352201461792</v>
+        <v>20.84870004653931</v>
       </c>
       <c r="J8" t="n">
-        <v>383</v>
+        <v>450</v>
       </c>
       <c r="K8" t="n">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="L8" t="n">
-        <v>488</v>
+        <v>453</v>
       </c>
       <c r="M8" t="n">
-        <v>6783.365868239699</v>
+        <v>5971.327291865444</v>
       </c>
       <c r="N8" t="n">
-        <v>4.283299207687378</v>
+        <v>6.776923179626465</v>
       </c>
       <c r="O8" t="n">
-        <v>1876</v>
+        <v>2682</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>6034</v>
+        <v>8256</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8176078697640927</v>
+        <v>0.8024118421345057</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6162773662044334</v>
+        <v>0.6679463159724192</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1232.069540903774</v>
+        <v>1241.958024626585</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4417312145233154</v>
+        <v>5.817899942398071</v>
       </c>
       <c r="E9" t="n">
-        <v>349</v>
+        <v>399</v>
       </c>
       <c r="F9" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H9" t="n">
-        <v>2557.555271223759</v>
+        <v>1965.456009203584</v>
       </c>
       <c r="I9" t="n">
-        <v>1.650887012481689</v>
+        <v>22.2516770362854</v>
       </c>
       <c r="J9" t="n">
-        <v>391</v>
+        <v>459</v>
       </c>
       <c r="K9" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>496</v>
+        <v>455</v>
       </c>
       <c r="M9" t="n">
-        <v>6629.091426768156</v>
+        <v>5876.102961592872</v>
       </c>
       <c r="N9" t="n">
-        <v>4.411617040634155</v>
+        <v>5.373180866241455</v>
       </c>
       <c r="O9" t="n">
-        <v>1837</v>
+        <v>2644</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>5972</v>
+        <v>8046</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8141420201373752</v>
+        <v>0.7886425692769141</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6141921861423731</v>
+        <v>0.6655170915060353</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1329.225015239653</v>
+        <v>1194.267540010658</v>
       </c>
       <c r="D10" t="n">
-        <v>0.400803804397583</v>
+        <v>3.461688995361328</v>
       </c>
       <c r="E10" t="n">
-        <v>306</v>
+        <v>365</v>
       </c>
       <c r="F10" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H10" t="n">
-        <v>2541.940419791255</v>
+        <v>2031.89168743701</v>
       </c>
       <c r="I10" t="n">
-        <v>1.371312141418457</v>
+        <v>23.25010514259338</v>
       </c>
       <c r="J10" t="n">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="K10" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="L10" t="n">
-        <v>485</v>
+        <v>440</v>
       </c>
       <c r="M10" t="n">
-        <v>6645.324215778717</v>
+        <v>5899.154885580174</v>
       </c>
       <c r="N10" t="n">
-        <v>4.783370018005371</v>
+        <v>6.535601854324341</v>
       </c>
       <c r="O10" t="n">
-        <v>1855</v>
+        <v>2652</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>5969</v>
+        <v>8146</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7999758970249293</v>
+        <v>0.7975527743931742</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6174843638545657</v>
+        <v>0.6555622412281897</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1336.716932236002</v>
+        <v>1144.571991102302</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5677671432495117</v>
+        <v>4.527960062026978</v>
       </c>
       <c r="E11" t="n">
-        <v>329</v>
+        <v>385</v>
       </c>
       <c r="F11" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="G11" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H11" t="n">
-        <v>2611.311568436733</v>
+        <v>1976.384901919833</v>
       </c>
       <c r="I11" t="n">
-        <v>1.48668098449707</v>
+        <v>28.00229907035828</v>
       </c>
       <c r="J11" t="n">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="K11" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="L11" t="n">
-        <v>509</v>
+        <v>448</v>
       </c>
       <c r="M11" t="n">
-        <v>6665.244531666172</v>
+        <v>5867.662135963821</v>
       </c>
       <c r="N11" t="n">
-        <v>4.065323114395142</v>
+        <v>6.71779990196228</v>
       </c>
       <c r="O11" t="n">
-        <v>1857</v>
+        <v>2666</v>
       </c>
       <c r="P11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
-        <v>5972</v>
+        <v>8173</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7994496787199117</v>
+        <v>0.8049356004860879</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6082196900607997</v>
+        <v>0.6631733634071634</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1280.787951914605</v>
+        <v>1210.492208930622</v>
       </c>
       <c r="D12" t="n">
-        <v>0.424616813659668</v>
+        <v>3.936718225479126</v>
       </c>
       <c r="E12" t="n">
-        <v>326</v>
+        <v>375</v>
       </c>
       <c r="F12" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H12" t="n">
-        <v>2363.444979456247</v>
+        <v>1947.087652974257</v>
       </c>
       <c r="I12" t="n">
-        <v>1.597348213195801</v>
+        <v>23.97310614585876</v>
       </c>
       <c r="J12" t="n">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="K12" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="L12" t="n">
-        <v>485</v>
+        <v>430</v>
       </c>
       <c r="M12" t="n">
-        <v>6773.555914108541</v>
+        <v>5944.348609859489</v>
       </c>
       <c r="N12" t="n">
-        <v>4.622792959213257</v>
+        <v>6.747357845306396</v>
       </c>
       <c r="O12" t="n">
-        <v>1830</v>
+        <v>2659</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>5827</v>
+        <v>8115</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8109135041984565</v>
+        <v>0.7963625136448321</v>
       </c>
       <c r="S12" t="n">
-        <v>0.651077660031792</v>
+        <v>0.672447263650595</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1380.413477519933</v>
+        <v>1166.735755602587</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4460828304290771</v>
+        <v>4.581000804901123</v>
       </c>
       <c r="E13" t="n">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="G13" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="H13" t="n">
-        <v>2483.107519268838</v>
+        <v>2021.400283828133</v>
       </c>
       <c r="I13" t="n">
-        <v>1.345623970031738</v>
+        <v>26.46145510673523</v>
       </c>
       <c r="J13" t="n">
-        <v>343</v>
+        <v>446</v>
       </c>
       <c r="K13" t="n">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="L13" t="n">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="M13" t="n">
-        <v>6720.418738482601</v>
+        <v>5849.263712767716</v>
       </c>
       <c r="N13" t="n">
-        <v>4.880896091461182</v>
+        <v>5.966217994689941</v>
       </c>
       <c r="O13" t="n">
-        <v>1836</v>
+        <v>2693</v>
       </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>5911</v>
+        <v>8309</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7945941270570864</v>
+        <v>0.8005328853517329</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6305129760665037</v>
+        <v>0.6544179946245474</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1258.180352304326</v>
+        <v>1101.700183675447</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4499790668487549</v>
+        <v>3.012331008911133</v>
       </c>
       <c r="E14" t="n">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="H14" t="n">
-        <v>2713.350654384679</v>
+        <v>2076.591646041566</v>
       </c>
       <c r="I14" t="n">
-        <v>2.201789140701294</v>
+        <v>23.53084397315979</v>
       </c>
       <c r="J14" t="n">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="K14" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L14" t="n">
-        <v>533</v>
+        <v>463</v>
       </c>
       <c r="M14" t="n">
-        <v>6571.923819672908</v>
+        <v>5880.87089330408</v>
       </c>
       <c r="N14" t="n">
-        <v>6.990218162536621</v>
+        <v>5.212737083435059</v>
       </c>
       <c r="O14" t="n">
-        <v>1868</v>
+        <v>2645</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>6004</v>
+        <v>8044</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8085522007211965</v>
+        <v>0.8126637697607278</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5871299289467836</v>
+        <v>0.6468904548804227</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1303.242478529018</v>
+        <v>1130.402620787567</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7212138175964355</v>
+        <v>2.930315017700195</v>
       </c>
       <c r="E15" t="n">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="G15" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="H15" t="n">
-        <v>2585.355257817256</v>
+        <v>2035.515968436668</v>
       </c>
       <c r="I15" t="n">
-        <v>2.459205150604248</v>
+        <v>26.51208591461182</v>
       </c>
       <c r="J15" t="n">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="K15" t="n">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="L15" t="n">
-        <v>501</v>
+        <v>442</v>
       </c>
       <c r="M15" t="n">
-        <v>6830.411610791586</v>
+        <v>5941.619294476308</v>
       </c>
       <c r="N15" t="n">
-        <v>8.741134643554688</v>
+        <v>5.138058185577393</v>
       </c>
       <c r="O15" t="n">
-        <v>1844</v>
+        <v>2705</v>
       </c>
       <c r="P15" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>5806</v>
+        <v>8214</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8092000083172171</v>
+        <v>0.809748392691794</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6214934904168045</v>
+        <v>0.6574139359064948</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1321.68134903643</v>
+        <v>1179.934606260623</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4761216640472412</v>
+        <v>4.142369985580444</v>
       </c>
       <c r="E16" t="n">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="F16" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H16" t="n">
-        <v>2525.977433087231</v>
+        <v>2026.078646371521</v>
       </c>
       <c r="I16" t="n">
-        <v>1.528016328811646</v>
+        <v>21.50291919708252</v>
       </c>
       <c r="J16" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="K16" t="n">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="L16" t="n">
-        <v>529</v>
+        <v>432</v>
       </c>
       <c r="M16" t="n">
-        <v>6865.974061112879</v>
+        <v>5848.063549375045</v>
       </c>
       <c r="N16" t="n">
-        <v>4.711095809936523</v>
+        <v>4.8327317237854</v>
       </c>
       <c r="O16" t="n">
-        <v>1847</v>
+        <v>2655</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>5854</v>
+        <v>8083</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8075027174189172</v>
+        <v>0.7982349890184217</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6321021007938669</v>
+        <v>0.6535470879778591</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1196.912356882584</v>
+        <v>1210.606260166056</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4333791732788086</v>
+        <v>3.361767768859863</v>
       </c>
       <c r="E17" t="n">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="H17" t="n">
-        <v>2353.37761267622</v>
+        <v>1974.02382251229</v>
       </c>
       <c r="I17" t="n">
-        <v>1.313172817230225</v>
+        <v>20.48444414138794</v>
       </c>
       <c r="J17" t="n">
-        <v>370</v>
+        <v>422</v>
       </c>
       <c r="K17" t="n">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="L17" t="n">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="M17" t="n">
-        <v>6672.013562208589</v>
+        <v>6006.956575339312</v>
       </c>
       <c r="N17" t="n">
-        <v>4.170817852020264</v>
+        <v>7.183972835540771</v>
       </c>
       <c r="O17" t="n">
-        <v>1872</v>
+        <v>2668</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>5972</v>
+        <v>8049</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8206070257917194</v>
+        <v>0.7984659544342264</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6472762546517969</v>
+        <v>0.6713770446391508</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1326.054416358324</v>
+        <v>1190.028301210644</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5483331680297852</v>
+        <v>4.834075212478638</v>
       </c>
       <c r="E18" t="n">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="F18" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H18" t="n">
-        <v>2413.460638908428</v>
+        <v>1943.856806705803</v>
       </c>
       <c r="I18" t="n">
-        <v>1.568781137466431</v>
+        <v>20.69769096374512</v>
       </c>
       <c r="J18" t="n">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="K18" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>485</v>
+        <v>422</v>
       </c>
       <c r="M18" t="n">
-        <v>6712.451968184781</v>
+        <v>5919.527898497912</v>
       </c>
       <c r="N18" t="n">
-        <v>4.264580011367798</v>
+        <v>7.941004991531372</v>
       </c>
       <c r="O18" t="n">
-        <v>1922</v>
+        <v>2685</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>6112</v>
+        <v>8151</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8024485802440799</v>
+        <v>0.7989656740172445</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6404502184376762</v>
+        <v>0.6716196223690306</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1353.313015762897</v>
+        <v>1167.742279832631</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4515867233276367</v>
+        <v>3.563892126083374</v>
       </c>
       <c r="E19" t="n">
-        <v>339</v>
+        <v>381</v>
       </c>
       <c r="F19" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="H19" t="n">
-        <v>2528.804781373612</v>
+        <v>2069.312655481355</v>
       </c>
       <c r="I19" t="n">
-        <v>1.509500980377197</v>
+        <v>22.11116886138916</v>
       </c>
       <c r="J19" t="n">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="K19" t="n">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L19" t="n">
-        <v>507</v>
+        <v>445</v>
       </c>
       <c r="M19" t="n">
-        <v>6876.140405414227</v>
+        <v>5899.265398845218</v>
       </c>
       <c r="N19" t="n">
-        <v>5.875421047210693</v>
+        <v>5.598880052566528</v>
       </c>
       <c r="O19" t="n">
-        <v>1894</v>
+        <v>2694</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>6110</v>
+        <v>8294</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8031871171947992</v>
+        <v>0.8020529335633524</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6322348538167651</v>
+        <v>0.6492253669607027</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1383.606174033685</v>
+        <v>1144.53648666067</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4536681175231934</v>
+        <v>4.481624841690063</v>
       </c>
       <c r="E20" t="n">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c r="F20" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="G20" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="H20" t="n">
-        <v>2421.888285608982</v>
+        <v>2075.334369982484</v>
       </c>
       <c r="I20" t="n">
-        <v>1.597671985626221</v>
+        <v>22.92353105545044</v>
       </c>
       <c r="J20" t="n">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="K20" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="L20" t="n">
-        <v>491</v>
+        <v>434</v>
       </c>
       <c r="M20" t="n">
-        <v>6725.18869984845</v>
+        <v>5998.026604405243</v>
       </c>
       <c r="N20" t="n">
-        <v>5.990477085113525</v>
+        <v>4.584408283233643</v>
       </c>
       <c r="O20" t="n">
-        <v>1890</v>
+        <v>2715</v>
       </c>
       <c r="P20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>6060</v>
+        <v>8198</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7942650777866108</v>
+        <v>0.8091811587130897</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6398780177478799</v>
+        <v>0.6539971382490607</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1311.535848213854</v>
+        <v>1200.75364670438</v>
       </c>
       <c r="D21" t="n">
-        <v>1.048964738845825</v>
+        <v>4.307168960571289</v>
       </c>
       <c r="E21" t="n">
-        <v>344</v>
+        <v>404</v>
       </c>
       <c r="F21" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="G21" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="H21" t="n">
-        <v>2594.302182411313</v>
+        <v>2084.118587027309</v>
       </c>
       <c r="I21" t="n">
-        <v>1.52004599571228</v>
+        <v>24.31640005111694</v>
       </c>
       <c r="J21" t="n">
-        <v>410</v>
+        <v>439</v>
       </c>
       <c r="K21" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="L21" t="n">
-        <v>507</v>
+        <v>447</v>
       </c>
       <c r="M21" t="n">
-        <v>6958.681337251174</v>
+        <v>5910.432809885989</v>
       </c>
       <c r="N21" t="n">
-        <v>4.767052173614502</v>
+        <v>7.260672092437744</v>
       </c>
       <c r="O21" t="n">
-        <v>1901</v>
+        <v>2632</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>6078</v>
+        <v>8081</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8115252323464005</v>
+        <v>0.7968416721198557</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6271847988607399</v>
+        <v>0.6473830844432675</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1314.356895491647</v>
+        <v>1160.229582446619</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4192750453948975</v>
+        <v>5.148711204528809</v>
       </c>
       <c r="E22" t="n">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="F22" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="G22" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="H22" t="n">
-        <v>2615.37209295715</v>
+        <v>2047.093920168474</v>
       </c>
       <c r="I22" t="n">
-        <v>1.851637840270996</v>
+        <v>29.07561993598938</v>
       </c>
       <c r="J22" t="n">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="K22" t="n">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="L22" t="n">
-        <v>504</v>
+        <v>432</v>
       </c>
       <c r="M22" t="n">
-        <v>6813.510712879184</v>
+        <v>5887.821334425135</v>
       </c>
       <c r="N22" t="n">
-        <v>7.178903102874756</v>
+        <v>5.052422046661377</v>
       </c>
       <c r="O22" t="n">
-        <v>1841</v>
+        <v>2707</v>
       </c>
       <c r="P22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>5880</v>
+        <v>8289</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8070954973319122</v>
+        <v>0.8029441593849078</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6161491185427412</v>
+        <v>0.6523172487929536</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1294.607214555554</v>
+        <v>1124.472144187742</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4923291206359863</v>
+        <v>3.436884880065918</v>
       </c>
       <c r="E23" t="n">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="F23" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="H23" t="n">
-        <v>2545.800627302835</v>
+        <v>1860.738850585542</v>
       </c>
       <c r="I23" t="n">
-        <v>1.692148923873901</v>
+        <v>24.49884915351868</v>
       </c>
       <c r="J23" t="n">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="K23" t="n">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="L23" t="n">
-        <v>502</v>
+        <v>404</v>
       </c>
       <c r="M23" t="n">
-        <v>6798.345613643816</v>
+        <v>5898.234351106755</v>
       </c>
       <c r="N23" t="n">
-        <v>5.323745012283325</v>
+        <v>9.471729040145874</v>
       </c>
       <c r="O23" t="n">
-        <v>1910</v>
+        <v>2681</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>6164</v>
+        <v>8154</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8095702560403276</v>
+        <v>0.8093544479159693</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6255264483474352</v>
+        <v>0.6845261242906718</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1259.567021047533</v>
+        <v>1115.07550679212</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5704250335693359</v>
+        <v>6.665755748748779</v>
       </c>
       <c r="E24" t="n">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="F24" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="G24" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H24" t="n">
-        <v>2419.37161676436</v>
+        <v>2086.441737055186</v>
       </c>
       <c r="I24" t="n">
-        <v>1.799832820892334</v>
+        <v>23.59331083297729</v>
       </c>
       <c r="J24" t="n">
-        <v>400</v>
+        <v>438</v>
       </c>
       <c r="K24" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="L24" t="n">
-        <v>502</v>
+        <v>434</v>
       </c>
       <c r="M24" t="n">
-        <v>6724.431657593133</v>
+        <v>5980.705827513229</v>
       </c>
       <c r="N24" t="n">
-        <v>4.562457799911499</v>
+        <v>4.669135093688965</v>
       </c>
       <c r="O24" t="n">
-        <v>1839</v>
+        <v>2691</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q24" t="n">
-        <v>5872</v>
+        <v>8143</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8126879585986648</v>
+        <v>0.8135545303595434</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6402117323874592</v>
+        <v>0.651137876158887</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1400.517682025773</v>
+        <v>1272.892467962502</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4214668273925781</v>
+        <v>4.627491235733032</v>
       </c>
       <c r="E25" t="n">
-        <v>327</v>
+        <v>384</v>
       </c>
       <c r="F25" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="G25" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H25" t="n">
-        <v>2618.714225479083</v>
+        <v>1967.084903633623</v>
       </c>
       <c r="I25" t="n">
-        <v>1.456197261810303</v>
+        <v>18.53422021865845</v>
       </c>
       <c r="J25" t="n">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="K25" t="n">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="L25" t="n">
-        <v>500</v>
+        <v>419</v>
       </c>
       <c r="M25" t="n">
-        <v>6796.423208695617</v>
+        <v>5904.144380153131</v>
       </c>
       <c r="N25" t="n">
-        <v>4.465500116348267</v>
+        <v>5.287052869796753</v>
       </c>
       <c r="O25" t="n">
-        <v>1855</v>
+        <v>2719</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>5937</v>
+        <v>8303</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7939331264371684</v>
+        <v>0.7844069545044752</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6146922954814534</v>
+        <v>0.6668298102183938</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1415.490936900026</v>
+        <v>1212.995550441068</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4334402084350586</v>
+        <v>3.437386989593506</v>
       </c>
       <c r="E26" t="n">
-        <v>316</v>
+        <v>390</v>
       </c>
       <c r="F26" t="n">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="G26" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="H26" t="n">
-        <v>2536.642912044913</v>
+        <v>2026.427033263107</v>
       </c>
       <c r="I26" t="n">
-        <v>1.552158117294312</v>
+        <v>23.77768588066101</v>
       </c>
       <c r="J26" t="n">
-        <v>388</v>
+        <v>447</v>
       </c>
       <c r="K26" t="n">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="L26" t="n">
-        <v>493</v>
+        <v>449</v>
       </c>
       <c r="M26" t="n">
-        <v>6717.816469050188</v>
+        <v>5874.763015169412</v>
       </c>
       <c r="N26" t="n">
-        <v>4.765212059020996</v>
+        <v>5.991569995880127</v>
       </c>
       <c r="O26" t="n">
-        <v>1835</v>
+        <v>2658</v>
       </c>
       <c r="P26" t="n">
         <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>5812</v>
+        <v>8114</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7892930026562398</v>
+        <v>0.79352434348263</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6224006827617961</v>
+        <v>0.6550623356158187</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1238.162929929886</v>
+        <v>1197.300549835934</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5780978202819824</v>
+        <v>3.37415599822998</v>
       </c>
       <c r="E27" t="n">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="F27" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="G27" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H27" t="n">
-        <v>2627.744862194622</v>
+        <v>2087.333528560284</v>
       </c>
       <c r="I27" t="n">
-        <v>1.53729510307312</v>
+        <v>25.94460105895996</v>
       </c>
       <c r="J27" t="n">
-        <v>388</v>
+        <v>435</v>
       </c>
       <c r="K27" t="n">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="L27" t="n">
-        <v>499</v>
+        <v>445</v>
       </c>
       <c r="M27" t="n">
-        <v>6837.761675330029</v>
+        <v>5907.830485188858</v>
       </c>
       <c r="N27" t="n">
-        <v>4.61408805847168</v>
+        <v>8.875751972198486</v>
       </c>
       <c r="O27" t="n">
-        <v>1862</v>
+        <v>2651</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>5824</v>
+        <v>8064</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8189227719946638</v>
+        <v>0.7973366783563595</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6157010163610604</v>
+        <v>0.6466835780421758</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1256.035409717388</v>
+        <v>1169.283960813551</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5242509841918945</v>
+        <v>3.930951833724976</v>
       </c>
       <c r="E28" t="n">
-        <v>317</v>
+        <v>364</v>
       </c>
       <c r="F28" t="n">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="G28" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="H28" t="n">
-        <v>2539.387903463683</v>
+        <v>1865.239689305924</v>
       </c>
       <c r="I28" t="n">
-        <v>1.888245820999146</v>
+        <v>17.19810914993286</v>
       </c>
       <c r="J28" t="n">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="K28" t="n">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="L28" t="n">
-        <v>510</v>
+        <v>404</v>
       </c>
       <c r="M28" t="n">
-        <v>6717.897155668126</v>
+        <v>5869.137217013024</v>
       </c>
       <c r="N28" t="n">
-        <v>4.50947093963623</v>
+        <v>4.860640048980713</v>
       </c>
       <c r="O28" t="n">
-        <v>1823</v>
+        <v>2601</v>
       </c>
       <c r="P28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q28" t="n">
-        <v>5750</v>
+        <v>7966</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8130314619869364</v>
+        <v>0.8007741312600229</v>
       </c>
       <c r="S28" t="n">
-        <v>0.621996609263196</v>
+        <v>0.6821952494313638</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1540.228162913785</v>
+        <v>1199.492012698398</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4471697807312012</v>
+        <v>3.903197050094604</v>
       </c>
       <c r="E29" t="n">
-        <v>315</v>
+        <v>391</v>
       </c>
       <c r="F29" t="n">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="G29" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H29" t="n">
-        <v>2505.018275095357</v>
+        <v>1972.145154110999</v>
       </c>
       <c r="I29" t="n">
-        <v>1.570763111114502</v>
+        <v>19.31497478485107</v>
       </c>
       <c r="J29" t="n">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="K29" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="L29" t="n">
-        <v>494</v>
+        <v>434</v>
       </c>
       <c r="M29" t="n">
-        <v>6842.989168240663</v>
+        <v>5903.977114524842</v>
       </c>
       <c r="N29" t="n">
-        <v>5.226751089096069</v>
+        <v>4.538148164749146</v>
       </c>
       <c r="O29" t="n">
-        <v>1856</v>
+        <v>2668</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="n">
-        <v>5858</v>
+        <v>8238</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7749188074033181</v>
+        <v>0.7968332211607949</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6339292356735676</v>
+        <v>0.665963279352969</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1417.150589164109</v>
+        <v>1215.045786582491</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4172122478485107</v>
+        <v>3.097743988037109</v>
       </c>
       <c r="E30" t="n">
-        <v>300</v>
+        <v>377</v>
       </c>
       <c r="F30" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="H30" t="n">
-        <v>2480.99529508506</v>
+        <v>2068.263668770101</v>
       </c>
       <c r="I30" t="n">
-        <v>1.519554138183594</v>
+        <v>17.98866605758667</v>
       </c>
       <c r="J30" t="n">
-        <v>343</v>
+        <v>428</v>
       </c>
       <c r="K30" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="L30" t="n">
-        <v>470</v>
+        <v>432</v>
       </c>
       <c r="M30" t="n">
-        <v>6766.934866808652</v>
+        <v>5976.385530085873</v>
       </c>
       <c r="N30" t="n">
-        <v>4.828691005706787</v>
+        <v>4.830810070037842</v>
       </c>
       <c r="O30" t="n">
-        <v>1892</v>
+        <v>2679</v>
       </c>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>6172</v>
+        <v>8184</v>
       </c>
       <c r="R30" t="n">
-        <v>0.7905771790245633</v>
+        <v>0.7966922012534502</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6333649807604667</v>
+        <v>0.6539273347814992</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1265.576491857388</v>
+        <v>1224.367149087847</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5466482639312744</v>
+        <v>3.505983114242554</v>
       </c>
       <c r="E31" t="n">
-        <v>303</v>
+        <v>383</v>
       </c>
       <c r="F31" t="n">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="G31" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H31" t="n">
-        <v>2402.044178092155</v>
+        <v>2046.824918780427</v>
       </c>
       <c r="I31" t="n">
-        <v>1.48201584815979</v>
+        <v>18.97514510154724</v>
       </c>
       <c r="J31" t="n">
-        <v>356</v>
+        <v>442</v>
       </c>
       <c r="K31" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="L31" t="n">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="M31" t="n">
-        <v>6735.175187071211</v>
+        <v>5905.37003366103</v>
       </c>
       <c r="N31" t="n">
-        <v>5.01838493347168</v>
+        <v>4.310895919799805</v>
       </c>
       <c r="O31" t="n">
-        <v>1852</v>
+        <v>2642</v>
       </c>
       <c r="P31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>5901</v>
+        <v>8050</v>
       </c>
       <c r="R31" t="n">
-        <v>0.81209449543543</v>
+        <v>0.7926688518909286</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6433583223339016</v>
+        <v>0.653395992611237</v>
       </c>
     </row>
   </sheetData>
